--- a/agent_runs/manjidiwang/episodes/ep16/storyboard_index.xlsx
+++ b/agent_runs/manjidiwang/episodes/ep16/storyboard_index.xlsx
@@ -84,7 +84,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>审讯室开局施压（，总时长：12秒，镜头数：6个）</t>
+          <t>审讯室开局施压</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -132,7 +132,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>录音逼出红星厂秘密（，总时长：15秒，镜头数：4个）</t>
+          <t>录音逼出红星厂秘密</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -180,7 +180,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>病房醒来交出密钥信息（，总时长：15秒，镜头数：6个）</t>
+          <t>病房醒来交出密钥信息</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -228,7 +228,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>破解密钥后的警告（，总时长：10秒，镜头数：4个）</t>
+          <t>破解密钥后的警告</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -276,7 +276,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>总裁办下达焚厂命令（，总时长：12秒，镜头数：6个）</t>
+          <t>总裁办下达焚厂命令</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -324,7 +324,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>火灾灭口与离岸转账（，总时长：10秒，镜头数：4个）</t>
+          <t>火灾灭口与离岸转账</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -372,7 +372,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>田立民锁定新棋子（，总时长：12秒，镜头数：4个）</t>
+          <t>田立民锁定新棋子</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -420,7 +420,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>海外电话暴露朱天和软肋（，总时长：14秒，镜头数：5个）</t>
+          <t>海外电话暴露朱天和软肋</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -468,7 +468,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>田立民爆发野心（，总时长：13秒，镜头数：5个）</t>
+          <t>田立民爆发野心</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
